--- a/tests/fixtures/banks/synthetic/sbi-retail-synthetic.xlsx
+++ b/tests/fixtures/banks/synthetic/sbi-retail-synthetic.xlsx
@@ -648,13 +648,13 @@
         <v>ACH123456</v>
       </c>
       <c r="E18" t="str">
-        <v/>
+        <v>10,000.00</v>
       </c>
       <c r="F18" t="str">
-        <v>10,000.00</v>
+        <v/>
       </c>
       <c r="G18" t="str">
-        <v>6,62,900.00</v>
+        <v>6,42,900.00</v>
       </c>
     </row>
     <row r="19">
@@ -677,7 +677,7 @@
         <v/>
       </c>
       <c r="G19" t="str">
-        <v>6,61,950.00</v>
+        <v>6,41,950.00</v>
       </c>
     </row>
     <row r="20">
@@ -700,7 +700,7 @@
         <v>1,30,000.00</v>
       </c>
       <c r="G20" t="str">
-        <v>7,91,950.00</v>
+        <v>7,71,950.00</v>
       </c>
     </row>
     <row r="21">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="G21" t="str">
-        <v>7,31,950.00</v>
+        <v>7,11,950.00</v>
       </c>
     </row>
     <row r="22">
@@ -746,7 +746,7 @@
         <v>3,500.00</v>
       </c>
       <c r="G22" t="str">
-        <v>7,35,450.00</v>
+        <v>7,15,450.00</v>
       </c>
     </row>
     <row r="23">
@@ -769,7 +769,7 @@
         <v/>
       </c>
       <c r="G23" t="str">
-        <v>7,31,650.00</v>
+        <v>7,11,650.00</v>
       </c>
     </row>
     <row r="24">
@@ -792,7 +792,7 @@
         <v/>
       </c>
       <c r="G24" t="str">
-        <v>5,81,650.00</v>
+        <v>5,61,650.00</v>
       </c>
     </row>
     <row r="25">
@@ -815,7 +815,7 @@
         <v>85,000.00</v>
       </c>
       <c r="G25" t="str">
-        <v>6,66,650.00</v>
+        <v>6,46,650.00</v>
       </c>
     </row>
     <row r="26">
@@ -832,10 +832,10 @@
         <v/>
       </c>
       <c r="E26" t="str">
-        <v>2,36,850.00</v>
+        <v>2,46,850.00</v>
       </c>
       <c r="F26" t="str">
-        <v>8,03,500.00</v>
+        <v>7,93,500.00</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -846,7 +846,7 @@
         <v>Closing Balance: 6</v>
       </c>
       <c r="B27" t="str">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="C27" t="str">
         <v>650.00</v>
